--- a/notebooks/XGBoost/predictions_afr.xlsx
+++ b/notebooks/XGBoost/predictions_afr.xlsx
@@ -463,7 +463,7 @@
         <v>1.305</v>
       </c>
       <c r="D2" t="n">
-        <v>1.337920427322388</v>
+        <v>1.333839774131775</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         <v>1.49</v>
       </c>
       <c r="D3" t="n">
-        <v>1.496572375297546</v>
+        <v>1.502897381782532</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         <v>1.459</v>
       </c>
       <c r="D4" t="n">
-        <v>1.505865454673767</v>
+        <v>1.504938244819641</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>1.635</v>
       </c>
       <c r="D5" t="n">
-        <v>1.650961399078369</v>
+        <v>1.655352473258972</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         <v>1.123</v>
       </c>
       <c r="D6" t="n">
-        <v>1.141619086265564</v>
+        <v>1.140672922134399</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         <v>1.19</v>
       </c>
       <c r="D7" t="n">
-        <v>1.210875272750854</v>
+        <v>1.208008527755737</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         <v>1.147</v>
       </c>
       <c r="D8" t="n">
-        <v>1.131332993507385</v>
+        <v>1.142362356185913</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         <v>1.119</v>
       </c>
       <c r="D9" t="n">
-        <v>1.171207904815674</v>
+        <v>1.149627685546875</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         <v>1.391</v>
       </c>
       <c r="D10" t="n">
-        <v>1.416334271430969</v>
+        <v>1.415530920028687</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         <v>1.222</v>
       </c>
       <c r="D11" t="n">
-        <v>1.219371795654297</v>
+        <v>1.220258593559265</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         <v>1.559</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609597325325012</v>
+        <v>1.605180501937866</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         <v>1.548</v>
       </c>
       <c r="D13" t="n">
-        <v>1.602985858917236</v>
+        <v>1.61126708984375</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         <v>1.346</v>
       </c>
       <c r="D14" t="n">
-        <v>1.367660284042358</v>
+        <v>1.369040369987488</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         <v>1.65</v>
       </c>
       <c r="D15" t="n">
-        <v>1.688226342201233</v>
+        <v>1.686344385147095</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         <v>1.526</v>
       </c>
       <c r="D16" t="n">
-        <v>1.536739468574524</v>
+        <v>1.539897441864014</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         <v>1.183</v>
       </c>
       <c r="D17" t="n">
-        <v>1.22214674949646</v>
+        <v>1.222097277641296</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         <v>1.339</v>
       </c>
       <c r="D18" t="n">
-        <v>1.339912414550781</v>
+        <v>1.342038869857788</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>1.666</v>
       </c>
       <c r="D19" t="n">
-        <v>1.665318131446838</v>
+        <v>1.660814642906189</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         <v>1.34</v>
       </c>
       <c r="D20" t="n">
-        <v>1.328302979469299</v>
+        <v>1.337565064430237</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         <v>1.221</v>
       </c>
       <c r="D21" t="n">
-        <v>1.263764500617981</v>
+        <v>1.259890913963318</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         <v>1.473</v>
       </c>
       <c r="D22" t="n">
-        <v>1.526806235313416</v>
+        <v>1.501935958862305</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         <v>1.552</v>
       </c>
       <c r="D23" t="n">
-        <v>1.559346079826355</v>
+        <v>1.568055868148804</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         <v>1.532</v>
       </c>
       <c r="D24" t="n">
-        <v>1.535563826560974</v>
+        <v>1.537211894989014</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         <v>1.436</v>
       </c>
       <c r="D25" t="n">
-        <v>1.440383791923523</v>
+        <v>1.432950973510742</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         <v>1.642</v>
       </c>
       <c r="D26" t="n">
-        <v>1.691486954689026</v>
+        <v>1.690935492515564</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         <v>1.262</v>
       </c>
       <c r="D27" t="n">
-        <v>1.282421827316284</v>
+        <v>1.297560811042786</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         <v>0.88</v>
       </c>
       <c r="D28" t="n">
-        <v>1.043367624282837</v>
+        <v>1.02957284450531</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         <v>1.233</v>
       </c>
       <c r="D29" t="n">
-        <v>1.190237760543823</v>
+        <v>1.200989484786987</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         <v>1.34</v>
       </c>
       <c r="D30" t="n">
-        <v>1.414074182510376</v>
+        <v>1.414622187614441</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         <v>1.352</v>
       </c>
       <c r="D31" t="n">
-        <v>1.313364624977112</v>
+        <v>1.321791768074036</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         <v>1.451</v>
       </c>
       <c r="D32" t="n">
-        <v>1.468117952346802</v>
+        <v>1.457277655601501</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         <v>1.913</v>
       </c>
       <c r="D33" t="n">
-        <v>1.895154356956482</v>
+        <v>1.895996451377869</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         <v>1.309</v>
       </c>
       <c r="D34" t="n">
-        <v>1.303429484367371</v>
+        <v>1.302320599555969</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         <v>1.257</v>
       </c>
       <c r="D35" t="n">
-        <v>1.310843110084534</v>
+        <v>1.334379911422729</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         <v>1.492</v>
       </c>
       <c r="D36" t="n">
-        <v>1.511179566383362</v>
+        <v>1.506269812583923</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         <v>1.495</v>
       </c>
       <c r="D37" t="n">
-        <v>1.523179531097412</v>
+        <v>1.527469396591187</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         <v>1.502</v>
       </c>
       <c r="D38" t="n">
-        <v>1.505324006080627</v>
+        <v>1.507794976234436</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         <v>1.171</v>
       </c>
       <c r="D39" t="n">
-        <v>1.205562710762024</v>
+        <v>1.206899523735046</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         <v>1.198</v>
       </c>
       <c r="D40" t="n">
-        <v>1.207499623298645</v>
+        <v>1.206664562225342</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         <v>1.527</v>
       </c>
       <c r="D41" t="n">
-        <v>1.551984786987305</v>
+        <v>1.546822309494019</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         <v>1.444</v>
       </c>
       <c r="D42" t="n">
-        <v>1.444979310035706</v>
+        <v>1.436720013618469</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         <v>1.305</v>
       </c>
       <c r="D43" t="n">
-        <v>1.342618823051453</v>
+        <v>1.340447306632996</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         <v>1.346</v>
       </c>
       <c r="D44" t="n">
-        <v>1.344926357269287</v>
+        <v>1.360542893409729</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         <v>2.03</v>
       </c>
       <c r="D45" t="n">
-        <v>2.062210559844971</v>
+        <v>2.041936635971069</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         <v>1.414</v>
       </c>
       <c r="D46" t="n">
-        <v>1.417647838592529</v>
+        <v>1.415320038795471</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         <v>1.597</v>
       </c>
       <c r="D47" t="n">
-        <v>1.68144166469574</v>
+        <v>1.676596879959106</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>1.745</v>
       </c>
       <c r="D48" t="n">
-        <v>1.75649619102478</v>
+        <v>1.749820709228516</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         <v>1.806</v>
       </c>
       <c r="D49" t="n">
-        <v>1.850265264511108</v>
+        <v>1.84948718547821</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         <v>1.443</v>
       </c>
       <c r="D50" t="n">
-        <v>1.437607169151306</v>
+        <v>1.434778332710266</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         <v>1.534</v>
       </c>
       <c r="D51" t="n">
-        <v>1.555680394172668</v>
+        <v>1.54172956943512</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         <v>1.564</v>
       </c>
       <c r="D52" t="n">
-        <v>1.574738502502441</v>
+        <v>1.573360204696655</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         <v>1.419</v>
       </c>
       <c r="D53" t="n">
-        <v>1.43863046169281</v>
+        <v>1.439388275146484</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         <v>1.381</v>
       </c>
       <c r="D54" t="n">
-        <v>1.419756174087524</v>
+        <v>1.423412203788757</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         <v>1.047</v>
       </c>
       <c r="D55" t="n">
-        <v>1.051427006721497</v>
+        <v>1.074495077133179</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         <v>1.619</v>
       </c>
       <c r="D56" t="n">
-        <v>1.675428986549377</v>
+        <v>1.673079967498779</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>1.52</v>
       </c>
       <c r="D57" t="n">
-        <v>1.558199286460876</v>
+        <v>1.565747022628784</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         <v>1.454</v>
       </c>
       <c r="D58" t="n">
-        <v>1.449138879776001</v>
+        <v>1.44311535358429</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         <v>2.442</v>
       </c>
       <c r="D59" t="n">
-        <v>2.468364238739014</v>
+        <v>2.46750020980835</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         <v>1.522</v>
       </c>
       <c r="D60" t="n">
-        <v>1.549134850502014</v>
+        <v>1.552920699119568</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         <v>1.272</v>
       </c>
       <c r="D61" t="n">
-        <v>1.281533241271973</v>
+        <v>1.280271053314209</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         <v>1.104</v>
       </c>
       <c r="D62" t="n">
-        <v>1.123420000076294</v>
+        <v>1.129244565963745</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         <v>1.33</v>
       </c>
       <c r="D63" t="n">
-        <v>1.33734405040741</v>
+        <v>1.358695864677429</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         <v>1.103</v>
       </c>
       <c r="D64" t="n">
-        <v>1.117717504501343</v>
+        <v>1.120651364326477</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         <v>1.736</v>
       </c>
       <c r="D65" t="n">
-        <v>1.766652464866638</v>
+        <v>1.769927740097046</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         <v>1.551</v>
       </c>
       <c r="D66" t="n">
-        <v>1.564565539360046</v>
+        <v>1.571363091468811</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         <v>1.033</v>
       </c>
       <c r="D67" t="n">
-        <v>1.051446795463562</v>
+        <v>1.064295053482056</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         <v>1.297</v>
       </c>
       <c r="D68" t="n">
-        <v>1.289890766143799</v>
+        <v>1.274898290634155</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         <v>1.207</v>
       </c>
       <c r="D69" t="n">
-        <v>1.223431825637817</v>
+        <v>1.213012099266052</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         <v>1.278</v>
       </c>
       <c r="D70" t="n">
-        <v>1.288987755775452</v>
+        <v>1.289180755615234</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         <v>1.189</v>
       </c>
       <c r="D71" t="n">
-        <v>1.215021848678589</v>
+        <v>1.213262796401978</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         <v>1.179</v>
       </c>
       <c r="D72" t="n">
-        <v>1.138929486274719</v>
+        <v>1.135053157806396</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         <v>1.72</v>
       </c>
       <c r="D73" t="n">
-        <v>1.717436552047729</v>
+        <v>1.716985106468201</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         <v>1.399</v>
       </c>
       <c r="D74" t="n">
-        <v>1.43440854549408</v>
+        <v>1.43187403678894</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         <v>1.34</v>
       </c>
       <c r="D75" t="n">
-        <v>1.331917881965637</v>
+        <v>1.342366337776184</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         <v>1.463</v>
       </c>
       <c r="D76" t="n">
-        <v>1.520125508308411</v>
+        <v>1.519769430160522</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         <v>1.659</v>
       </c>
       <c r="D77" t="n">
-        <v>1.661167144775391</v>
+        <v>1.666265368461609</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         <v>1.471</v>
       </c>
       <c r="D78" t="n">
-        <v>1.452638626098633</v>
+        <v>1.472670197486877</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         <v>2.66</v>
       </c>
       <c r="D79" t="n">
-        <v>2.570323944091797</v>
+        <v>2.583139657974243</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         <v>1.402</v>
       </c>
       <c r="D80" t="n">
-        <v>1.424128174781799</v>
+        <v>1.423996806144714</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         <v>1.68</v>
       </c>
       <c r="D81" t="n">
-        <v>1.657158374786377</v>
+        <v>1.66799259185791</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         <v>1.946</v>
       </c>
       <c r="D82" t="n">
-        <v>1.927667737007141</v>
+        <v>1.936986327171326</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         <v>1.316</v>
       </c>
       <c r="D83" t="n">
-        <v>1.318983793258667</v>
+        <v>1.323512673377991</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         <v>1.424</v>
       </c>
       <c r="D84" t="n">
-        <v>1.415760040283203</v>
+        <v>1.43441641330719</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         <v>1.257</v>
       </c>
       <c r="D85" t="n">
-        <v>1.277809023857117</v>
+        <v>1.276313781738281</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         <v>0.976</v>
       </c>
       <c r="D86" t="n">
-        <v>1.071721196174622</v>
+        <v>1.074371457099915</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_afr.xlsx
+++ b/notebooks/XGBoost/predictions_afr.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР</t>
+          <t>СКР_прогноз</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>predictions</t>
+          <t>СКР_реальный</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_абсолютная</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Ошибка_относительная_%</t>
         </is>
       </c>
     </row>
@@ -457,13 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C2" t="n">
+        <v>1.361204504966736</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.305</v>
       </c>
-      <c r="D2" t="n">
-        <v>1.333839774131775</v>
+      <c r="E2" t="n">
+        <v>-0.0562045049667359</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-4.306858618140683</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C3" t="n">
+        <v>1.460216641426086</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.49</v>
       </c>
-      <c r="D3" t="n">
-        <v>1.502897381782532</v>
+      <c r="E3" t="n">
+        <v>0.02978335857391357</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.998883125766011</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +511,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="n">
+        <v>1.519587516784668</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.459</v>
       </c>
-      <c r="D4" t="n">
-        <v>1.504938244819641</v>
+      <c r="E4" t="n">
+        <v>-0.06058751678466789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-4.152674214165037</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
+        <v>1.645257830619812</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.635</v>
       </c>
-      <c r="D5" t="n">
-        <v>1.655352473258972</v>
+      <c r="E5" t="n">
+        <v>-0.010257830619812</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.6273902519762693</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +555,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="n">
+        <v>1.150643587112427</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.123</v>
       </c>
-      <c r="D6" t="n">
-        <v>1.140672922134399</v>
+      <c r="E6" t="n">
+        <v>-0.02764358711242676</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.46158389246899</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +577,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="n">
+        <v>1.21263587474823</v>
+      </c>
+      <c r="D7" t="n">
         <v>1.19</v>
       </c>
-      <c r="D7" t="n">
-        <v>1.208008527755737</v>
+      <c r="E7" t="n">
+        <v>-0.02263587474823003</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.902174348590759</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" t="n">
+        <v>1.148588299751282</v>
+      </c>
+      <c r="D8" t="n">
         <v>1.147</v>
       </c>
-      <c r="D8" t="n">
-        <v>1.142362356185913</v>
+      <c r="E8" t="n">
+        <v>-0.001588299751281719</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.138474259048101</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" t="n">
+        <v>1.161955714225769</v>
+      </c>
+      <c r="D9" t="n">
         <v>1.119</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.149627685546875</v>
+      <c r="E9" t="n">
+        <v>-0.04295571422576905</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.838759090774714</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" t="n">
+        <v>1.434039115905762</v>
+      </c>
+      <c r="D10" t="n">
         <v>1.391</v>
       </c>
-      <c r="D10" t="n">
-        <v>1.415530920028687</v>
+      <c r="E10" t="n">
+        <v>-0.0430391159057617</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.094113293009468</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" t="n">
+        <v>1.245630741119385</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.222</v>
       </c>
-      <c r="D11" t="n">
-        <v>1.220258593559265</v>
+      <c r="E11" t="n">
+        <v>-0.02363074111938479</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.933775869016759</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" t="n">
+        <v>1.627184987068176</v>
+      </c>
+      <c r="D12" t="n">
         <v>1.559</v>
       </c>
-      <c r="D12" t="n">
-        <v>1.605180501937866</v>
+      <c r="E12" t="n">
+        <v>-0.06818498706817633</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-4.373636117265961</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" t="n">
+        <v>1.64634895324707</v>
+      </c>
+      <c r="D13" t="n">
         <v>1.548</v>
       </c>
-      <c r="D13" t="n">
-        <v>1.61126708984375</v>
+      <c r="E13" t="n">
+        <v>-0.09834895324707027</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-6.353291553428312</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +731,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="n">
+        <v>1.387126922607422</v>
+      </c>
+      <c r="D14" t="n">
         <v>1.346</v>
       </c>
-      <c r="D14" t="n">
-        <v>1.369040369987488</v>
+      <c r="E14" t="n">
+        <v>-0.04112692260742179</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.055492021353773</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" t="n">
+        <v>1.707546591758728</v>
+      </c>
+      <c r="D15" t="n">
         <v>1.65</v>
       </c>
-      <c r="D15" t="n">
-        <v>1.686344385147095</v>
+      <c r="E15" t="n">
+        <v>-0.05754659175872812</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-3.487672227801704</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +775,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" t="n">
+        <v>1.545559525489807</v>
+      </c>
+      <c r="D16" t="n">
         <v>1.526</v>
       </c>
-      <c r="D16" t="n">
-        <v>1.539897441864014</v>
+      <c r="E16" t="n">
+        <v>-0.01955952548980711</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.281751342713441</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" t="n">
+        <v>1.275659441947937</v>
+      </c>
+      <c r="D17" t="n">
         <v>1.183</v>
       </c>
-      <c r="D17" t="n">
-        <v>1.222097277641296</v>
+      <c r="E17" t="n">
+        <v>-0.09265944194793696</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-7.832581736934655</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +819,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C18" t="n">
+        <v>1.334794163703918</v>
+      </c>
+      <c r="D18" t="n">
         <v>1.339</v>
       </c>
-      <c r="D18" t="n">
-        <v>1.342038869857788</v>
+      <c r="E18" t="n">
+        <v>0.004205836296081511</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3141027853682981</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +841,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C19" t="n">
+        <v>1.630613923072815</v>
+      </c>
+      <c r="D19" t="n">
         <v>1.666</v>
       </c>
-      <c r="D19" t="n">
-        <v>1.660814642906189</v>
+      <c r="E19" t="n">
+        <v>0.03538607692718498</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.124014221319627</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +863,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C20" t="n">
+        <v>1.30300498008728</v>
+      </c>
+      <c r="D20" t="n">
         <v>1.34</v>
       </c>
-      <c r="D20" t="n">
-        <v>1.337565064430237</v>
+      <c r="E20" t="n">
+        <v>0.03699501991271981</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.760822381546254</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" t="n">
+        <v>1.301377654075623</v>
+      </c>
+      <c r="D21" t="n">
         <v>1.221</v>
       </c>
-      <c r="D21" t="n">
-        <v>1.259890913963318</v>
+      <c r="E21" t="n">
+        <v>-0.08037765407562247</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-6.582936451729932</v>
       </c>
     </row>
     <row r="22">
@@ -777,13 +907,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C22" t="n">
+        <v>1.521060109138489</v>
+      </c>
+      <c r="D22" t="n">
         <v>1.473</v>
       </c>
-      <c r="D22" t="n">
-        <v>1.501935958862305</v>
+      <c r="E22" t="n">
+        <v>-0.04806010913848868</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.262736533502286</v>
       </c>
     </row>
     <row r="23">
@@ -793,13 +929,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C23" t="n">
+        <v>1.531676054000854</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.552</v>
       </c>
-      <c r="D23" t="n">
-        <v>1.568055868148804</v>
+      <c r="E23" t="n">
+        <v>0.02032394599914555</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.309532603037729</v>
       </c>
     </row>
     <row r="24">
@@ -809,13 +951,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C24" t="n">
+        <v>1.53467059135437</v>
+      </c>
+      <c r="D24" t="n">
         <v>1.532</v>
       </c>
-      <c r="D24" t="n">
-        <v>1.537211894989014</v>
+      <c r="E24" t="n">
+        <v>-0.002670591354370089</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.1743205844889092</v>
       </c>
     </row>
     <row r="25">
@@ -825,13 +973,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C25" t="n">
+        <v>1.434890627861023</v>
+      </c>
+      <c r="D25" t="n">
         <v>1.436</v>
       </c>
-      <c r="D25" t="n">
-        <v>1.432950973510742</v>
+      <c r="E25" t="n">
+        <v>0.001109372138976994</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.07725432722681017</v>
       </c>
     </row>
     <row r="26">
@@ -841,13 +995,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C26" t="n">
+        <v>1.725212931632996</v>
+      </c>
+      <c r="D26" t="n">
         <v>1.642</v>
       </c>
-      <c r="D26" t="n">
-        <v>1.690935492515564</v>
+      <c r="E26" t="n">
+        <v>-0.0832129316329957</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-5.067779027588045</v>
       </c>
     </row>
     <row r="27">
@@ -857,13 +1017,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C27" t="n">
+        <v>1.304234385490417</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.262</v>
       </c>
-      <c r="D27" t="n">
-        <v>1.297560811042786</v>
+      <c r="E27" t="n">
+        <v>-0.04223438549041747</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-3.346623255976028</v>
       </c>
     </row>
     <row r="28">
@@ -873,13 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C28" t="n">
+        <v>1.004217386245728</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.88</v>
       </c>
-      <c r="D28" t="n">
-        <v>1.02957284450531</v>
+      <c r="E28" t="n">
+        <v>-0.1242173862457275</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-14.11561207337813</v>
       </c>
     </row>
     <row r="29">
@@ -889,13 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C29" t="n">
+        <v>1.200892806053162</v>
+      </c>
+      <c r="D29" t="n">
         <v>1.233</v>
       </c>
-      <c r="D29" t="n">
-        <v>1.200989484786987</v>
+      <c r="E29" t="n">
+        <v>0.03210719394683847</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.603989776710338</v>
       </c>
     </row>
     <row r="30">
@@ -905,13 +1083,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C30" t="n">
+        <v>1.434365153312683</v>
+      </c>
+      <c r="D30" t="n">
         <v>1.34</v>
       </c>
-      <c r="D30" t="n">
-        <v>1.414622187614441</v>
+      <c r="E30" t="n">
+        <v>-0.09436515331268303</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-7.04217562034948</v>
       </c>
     </row>
     <row r="31">
@@ -921,13 +1105,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C31" t="n">
+        <v>1.32475483417511</v>
+      </c>
+      <c r="D31" t="n">
         <v>1.352</v>
       </c>
-      <c r="D31" t="n">
-        <v>1.321791768074036</v>
+      <c r="E31" t="n">
+        <v>0.02724516582489023</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.015174987048094</v>
       </c>
     </row>
     <row r="32">
@@ -937,13 +1127,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C32" t="n">
+        <v>1.46932852268219</v>
+      </c>
+      <c r="D32" t="n">
         <v>1.451</v>
       </c>
-      <c r="D32" t="n">
-        <v>1.457277655601501</v>
+      <c r="E32" t="n">
+        <v>-0.01832852268218987</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-1.26316489884148</v>
       </c>
     </row>
     <row r="33">
@@ -953,13 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C33" t="n">
+        <v>1.854299187660217</v>
+      </c>
+      <c r="D33" t="n">
         <v>1.913</v>
       </c>
-      <c r="D33" t="n">
-        <v>1.895996451377869</v>
+      <c r="E33" t="n">
+        <v>0.05870081233978275</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.068521293245309</v>
       </c>
     </row>
     <row r="34">
@@ -969,13 +1171,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C34" t="n">
+        <v>1.310773253440857</v>
+      </c>
+      <c r="D34" t="n">
         <v>1.309</v>
       </c>
-      <c r="D34" t="n">
-        <v>1.302320599555969</v>
+      <c r="E34" t="n">
+        <v>-0.001773253440856992</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.1354662674451484</v>
       </c>
     </row>
     <row r="35">
@@ -985,13 +1193,19 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C35" t="n">
+        <v>1.320708632469177</v>
+      </c>
+      <c r="D35" t="n">
         <v>1.257</v>
       </c>
-      <c r="D35" t="n">
-        <v>1.334379911422729</v>
+      <c r="E35" t="n">
+        <v>-0.06370863246917735</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-5.068308072329145</v>
       </c>
     </row>
     <row r="36">
@@ -1001,13 +1215,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C36" t="n">
+        <v>1.520466685295105</v>
+      </c>
+      <c r="D36" t="n">
         <v>1.492</v>
       </c>
-      <c r="D36" t="n">
-        <v>1.506269812583923</v>
+      <c r="E36" t="n">
+        <v>-0.02846668529510499</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-1.907954778492291</v>
       </c>
     </row>
     <row r="37">
@@ -1017,13 +1237,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C37" t="n">
+        <v>1.536909341812134</v>
+      </c>
+      <c r="D37" t="n">
         <v>1.495</v>
       </c>
-      <c r="D37" t="n">
-        <v>1.527469396591187</v>
+      <c r="E37" t="n">
+        <v>-0.04190934181213368</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-2.803300455661116</v>
       </c>
     </row>
     <row r="38">
@@ -1033,13 +1259,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C38" t="n">
+        <v>1.484651327133179</v>
+      </c>
+      <c r="D38" t="n">
         <v>1.502</v>
       </c>
-      <c r="D38" t="n">
-        <v>1.507794976234436</v>
+      <c r="E38" t="n">
+        <v>0.01734867286682129</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.155038140267729</v>
       </c>
     </row>
     <row r="39">
@@ -1049,13 +1281,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C39" t="n">
+        <v>1.232507824897766</v>
+      </c>
+      <c r="D39" t="n">
         <v>1.171</v>
       </c>
-      <c r="D39" t="n">
-        <v>1.206899523735046</v>
+      <c r="E39" t="n">
+        <v>-0.06150782489776607</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-5.252589658220843</v>
       </c>
     </row>
     <row r="40">
@@ -1065,13 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C40" t="n">
+        <v>1.203209638595581</v>
+      </c>
+      <c r="D40" t="n">
         <v>1.198</v>
       </c>
-      <c r="D40" t="n">
-        <v>1.206664562225342</v>
+      <c r="E40" t="n">
+        <v>-0.005209638595581101</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.4348613184959183</v>
       </c>
     </row>
     <row r="41">
@@ -1081,13 +1325,19 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C41" t="n">
+        <v>1.550869822502136</v>
+      </c>
+      <c r="D41" t="n">
         <v>1.527</v>
       </c>
-      <c r="D41" t="n">
-        <v>1.546822309494019</v>
+      <c r="E41" t="n">
+        <v>-0.02386982250213632</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-1.563184184815738</v>
       </c>
     </row>
     <row r="42">
@@ -1097,13 +1347,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C42" t="n">
+        <v>1.439392805099487</v>
+      </c>
+      <c r="D42" t="n">
         <v>1.444</v>
       </c>
-      <c r="D42" t="n">
-        <v>1.436720013618469</v>
+      <c r="E42" t="n">
+        <v>0.004607194900512646</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3190578185950586</v>
       </c>
     </row>
     <row r="43">
@@ -1113,13 +1369,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C43" t="n">
+        <v>1.362046122550964</v>
+      </c>
+      <c r="D43" t="n">
         <v>1.305</v>
       </c>
-      <c r="D43" t="n">
-        <v>1.340447306632996</v>
+      <c r="E43" t="n">
+        <v>-0.05704612255096442</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-4.371350387047082</v>
       </c>
     </row>
     <row r="44">
@@ -1129,13 +1391,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C44" t="n">
+        <v>1.320439338684082</v>
+      </c>
+      <c r="D44" t="n">
         <v>1.346</v>
       </c>
-      <c r="D44" t="n">
-        <v>1.360542893409729</v>
+      <c r="E44" t="n">
+        <v>0.02556066131591805</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.899009013069692</v>
       </c>
     </row>
     <row r="45">
@@ -1145,13 +1413,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C45" t="n">
+        <v>2.07588791847229</v>
+      </c>
+      <c r="D45" t="n">
         <v>2.03</v>
       </c>
-      <c r="D45" t="n">
-        <v>2.041936635971069</v>
+      <c r="E45" t="n">
+        <v>-0.04588791847229023</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-2.2604885946941</v>
       </c>
     </row>
     <row r="46">
@@ -1161,13 +1435,19 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C46" t="n">
+        <v>1.410475373268127</v>
+      </c>
+      <c r="D46" t="n">
         <v>1.414</v>
       </c>
-      <c r="D46" t="n">
-        <v>1.415320038795471</v>
+      <c r="E46" t="n">
+        <v>0.003524626731872482</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.2492663883926791</v>
       </c>
     </row>
     <row r="47">
@@ -1177,13 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C47" t="n">
+        <v>1.722460508346558</v>
+      </c>
+      <c r="D47" t="n">
         <v>1.597</v>
       </c>
-      <c r="D47" t="n">
-        <v>1.676596879959106</v>
+      <c r="E47" t="n">
+        <v>-0.1254605083465576</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-7.856011793773178</v>
       </c>
     </row>
     <row r="48">
@@ -1193,13 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C48" t="n">
+        <v>1.749882102012634</v>
+      </c>
+      <c r="D48" t="n">
         <v>1.745</v>
       </c>
-      <c r="D48" t="n">
-        <v>1.749820709228516</v>
+      <c r="E48" t="n">
+        <v>-0.004882102012634171</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-0.279776619635196</v>
       </c>
     </row>
     <row r="49">
@@ -1209,13 +1501,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C49" t="n">
+        <v>1.837307810783386</v>
+      </c>
+      <c r="D49" t="n">
         <v>1.806</v>
       </c>
-      <c r="D49" t="n">
-        <v>1.84948718547821</v>
+      <c r="E49" t="n">
+        <v>-0.03130781078338618</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-1.733544340165348</v>
       </c>
     </row>
     <row r="50">
@@ -1225,13 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C50" t="n">
+        <v>1.434138298034668</v>
+      </c>
+      <c r="D50" t="n">
         <v>1.443</v>
       </c>
-      <c r="D50" t="n">
-        <v>1.434778332710266</v>
+      <c r="E50" t="n">
+        <v>0.008861701965332092</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.6141165603140742</v>
       </c>
     </row>
     <row r="51">
@@ -1241,13 +1545,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C51" t="n">
+        <v>1.539367079734802</v>
+      </c>
+      <c r="D51" t="n">
         <v>1.534</v>
       </c>
-      <c r="D51" t="n">
-        <v>1.54172956943512</v>
+      <c r="E51" t="n">
+        <v>-0.005367079734802216</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.3498748197393882</v>
       </c>
     </row>
     <row r="52">
@@ -1257,13 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C52" t="n">
+        <v>1.557774901390076</v>
+      </c>
+      <c r="D52" t="n">
         <v>1.564</v>
       </c>
-      <c r="D52" t="n">
-        <v>1.573360204696655</v>
+      <c r="E52" t="n">
+        <v>0.006225098609924373</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.398024207795676</v>
       </c>
     </row>
     <row r="53">
@@ -1273,13 +1589,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C53" t="n">
+        <v>1.437110424041748</v>
+      </c>
+      <c r="D53" t="n">
         <v>1.419</v>
       </c>
-      <c r="D53" t="n">
-        <v>1.439388275146484</v>
+      <c r="E53" t="n">
+        <v>-0.01811042404174801</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-1.276280764041438</v>
       </c>
     </row>
     <row r="54">
@@ -1289,13 +1611,19 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C54" t="n">
+        <v>1.435223817825317</v>
+      </c>
+      <c r="D54" t="n">
         <v>1.381</v>
       </c>
-      <c r="D54" t="n">
-        <v>1.423412203788757</v>
+      <c r="E54" t="n">
+        <v>-0.05422381782531738</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-3.926416931594306</v>
       </c>
     </row>
     <row r="55">
@@ -1305,13 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C55" t="n">
+        <v>1.095302581787109</v>
+      </c>
+      <c r="D55" t="n">
         <v>1.047</v>
       </c>
-      <c r="D55" t="n">
-        <v>1.074495077133179</v>
+      <c r="E55" t="n">
+        <v>-0.04830258178710944</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-4.613427104786003</v>
       </c>
     </row>
     <row r="56">
@@ -1321,13 +1655,19 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C56" t="n">
+        <v>1.7225261926651</v>
+      </c>
+      <c r="D56" t="n">
         <v>1.619</v>
       </c>
-      <c r="D56" t="n">
-        <v>1.673079967498779</v>
+      <c r="E56" t="n">
+        <v>-0.1035261926651001</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-6.394452913224219</v>
       </c>
     </row>
     <row r="57">
@@ -1337,13 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C57" t="n">
+        <v>1.595932722091675</v>
+      </c>
+      <c r="D57" t="n">
         <v>1.52</v>
       </c>
-      <c r="D57" t="n">
-        <v>1.565747022628784</v>
+      <c r="E57" t="n">
+        <v>-0.07593272209167479</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-4.99557382182071</v>
       </c>
     </row>
     <row r="58">
@@ -1353,13 +1699,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C58" t="n">
+        <v>1.431061983108521</v>
+      </c>
+      <c r="D58" t="n">
         <v>1.454</v>
       </c>
-      <c r="D58" t="n">
-        <v>1.44311535358429</v>
+      <c r="E58" t="n">
+        <v>0.02293801689147945</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.577580253884419</v>
       </c>
     </row>
     <row r="59">
@@ -1369,13 +1721,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C59" t="n">
+        <v>2.456992149353027</v>
+      </c>
+      <c r="D59" t="n">
         <v>2.442</v>
       </c>
-      <c r="D59" t="n">
-        <v>2.46750020980835</v>
+      <c r="E59" t="n">
+        <v>-0.01499214935302717</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-0.6139291299355926</v>
       </c>
     </row>
     <row r="60">
@@ -1385,13 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C60" t="n">
+        <v>1.56514573097229</v>
+      </c>
+      <c r="D60" t="n">
         <v>1.522</v>
       </c>
-      <c r="D60" t="n">
-        <v>1.552920699119568</v>
+      <c r="E60" t="n">
+        <v>-0.04314573097229002</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-2.834804925906046</v>
       </c>
     </row>
     <row r="61">
@@ -1401,13 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C61" t="n">
+        <v>1.311789035797119</v>
+      </c>
+      <c r="D61" t="n">
         <v>1.272</v>
       </c>
-      <c r="D61" t="n">
-        <v>1.280271053314209</v>
+      <c r="E61" t="n">
+        <v>-0.03978903579711912</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-3.128068851974774</v>
       </c>
     </row>
     <row r="62">
@@ -1417,13 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C62" t="n">
+        <v>1.155730843544006</v>
+      </c>
+      <c r="D62" t="n">
         <v>1.104</v>
       </c>
-      <c r="D62" t="n">
-        <v>1.129244565963745</v>
+      <c r="E62" t="n">
+        <v>-0.05173084354400626</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-4.685764813768682</v>
       </c>
     </row>
     <row r="63">
@@ -1433,13 +1809,19 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C63" t="n">
+        <v>1.319729685783386</v>
+      </c>
+      <c r="D63" t="n">
         <v>1.33</v>
       </c>
-      <c r="D63" t="n">
-        <v>1.358695864677429</v>
+      <c r="E63" t="n">
+        <v>0.01027031421661384</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.7722040764371307</v>
       </c>
     </row>
     <row r="64">
@@ -1449,13 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C64" t="n">
+        <v>1.121143698692322</v>
+      </c>
+      <c r="D64" t="n">
         <v>1.103</v>
       </c>
-      <c r="D64" t="n">
-        <v>1.120651364326477</v>
+      <c r="E64" t="n">
+        <v>-0.0181436986923218</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-1.644940951253109</v>
       </c>
     </row>
     <row r="65">
@@ -1465,13 +1853,19 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C65" t="n">
+        <v>1.777756690979004</v>
+      </c>
+      <c r="D65" t="n">
         <v>1.736</v>
       </c>
-      <c r="D65" t="n">
-        <v>1.769927740097046</v>
+      <c r="E65" t="n">
+        <v>-0.04175669097900392</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-2.405339342108521</v>
       </c>
     </row>
     <row r="66">
@@ -1481,13 +1875,19 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C66" t="n">
+        <v>1.563356518745422</v>
+      </c>
+      <c r="D66" t="n">
         <v>1.551</v>
       </c>
-      <c r="D66" t="n">
-        <v>1.571363091468811</v>
+      <c r="E66" t="n">
+        <v>-0.01235651874542243</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-0.7966807701755273</v>
       </c>
     </row>
     <row r="67">
@@ -1497,13 +1897,19 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C67" t="n">
+        <v>1.096142530441284</v>
+      </c>
+      <c r="D67" t="n">
         <v>1.033</v>
       </c>
-      <c r="D67" t="n">
-        <v>1.064295053482056</v>
+      <c r="E67" t="n">
+        <v>-0.06314253044128426</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-6.112539248914256</v>
       </c>
     </row>
     <row r="68">
@@ -1513,13 +1919,19 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C68" t="n">
+        <v>1.28760302066803</v>
+      </c>
+      <c r="D68" t="n">
         <v>1.297</v>
       </c>
-      <c r="D68" t="n">
-        <v>1.274898290634155</v>
+      <c r="E68" t="n">
+        <v>0.009396979331970146</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.724516525209726</v>
       </c>
     </row>
     <row r="69">
@@ -1529,13 +1941,19 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C69" t="n">
+        <v>1.228188633918762</v>
+      </c>
+      <c r="D69" t="n">
         <v>1.207</v>
       </c>
-      <c r="D69" t="n">
-        <v>1.213012099266052</v>
+      <c r="E69" t="n">
+        <v>-0.02118863391876213</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-1.755479197909042</v>
       </c>
     </row>
     <row r="70">
@@ -1545,13 +1963,19 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C70" t="n">
+        <v>1.303571343421936</v>
+      </c>
+      <c r="D70" t="n">
         <v>1.278</v>
       </c>
-      <c r="D70" t="n">
-        <v>1.289180755615234</v>
+      <c r="E70" t="n">
+        <v>-0.02557134342193601</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-2.000887591700783</v>
       </c>
     </row>
     <row r="71">
@@ -1561,13 +1985,19 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C71" t="n">
+        <v>1.244389057159424</v>
+      </c>
+      <c r="D71" t="n">
         <v>1.189</v>
       </c>
-      <c r="D71" t="n">
-        <v>1.213262796401978</v>
+      <c r="E71" t="n">
+        <v>-0.05538905715942377</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-4.658457288429249</v>
       </c>
     </row>
     <row r="72">
@@ -1577,13 +2007,19 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C72" t="n">
+        <v>1.160467624664307</v>
+      </c>
+      <c r="D72" t="n">
         <v>1.179</v>
       </c>
-      <c r="D72" t="n">
-        <v>1.135053157806396</v>
+      <c r="E72" t="n">
+        <v>0.01853237533569341</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.571872377921409</v>
       </c>
     </row>
     <row r="73">
@@ -1593,13 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C73" t="n">
+        <v>1.719456434249878</v>
+      </c>
+      <c r="D73" t="n">
         <v>1.72</v>
       </c>
-      <c r="D73" t="n">
-        <v>1.716985106468201</v>
+      <c r="E73" t="n">
+        <v>0.0005435657501220437</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.0316026598908165</v>
       </c>
     </row>
     <row r="74">
@@ -1609,13 +2051,19 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C74" t="n">
+        <v>1.440039277076721</v>
+      </c>
+      <c r="D74" t="n">
         <v>1.399</v>
       </c>
-      <c r="D74" t="n">
-        <v>1.43187403678894</v>
+      <c r="E74" t="n">
+        <v>-0.04103927707672117</v>
+      </c>
+      <c r="F74" t="n">
+        <v>-2.933472271388218</v>
       </c>
     </row>
     <row r="75">
@@ -1625,13 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C75" t="n">
+        <v>1.358943343162537</v>
+      </c>
+      <c r="D75" t="n">
         <v>1.34</v>
       </c>
-      <c r="D75" t="n">
-        <v>1.342366337776184</v>
+      <c r="E75" t="n">
+        <v>-0.01894334316253654</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-1.413682325562428</v>
       </c>
     </row>
     <row r="76">
@@ -1641,13 +2095,19 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C76" t="n">
+        <v>1.527583003044128</v>
+      </c>
+      <c r="D76" t="n">
         <v>1.463</v>
       </c>
-      <c r="D76" t="n">
-        <v>1.519769430160522</v>
+      <c r="E76" t="n">
+        <v>-0.06458300304412834</v>
+      </c>
+      <c r="F76" t="n">
+        <v>-4.414422627759969</v>
       </c>
     </row>
     <row r="77">
@@ -1657,13 +2117,19 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C77" t="n">
+        <v>1.676014184951782</v>
+      </c>
+      <c r="D77" t="n">
         <v>1.659</v>
       </c>
-      <c r="D77" t="n">
-        <v>1.666265368461609</v>
+      <c r="E77" t="n">
+        <v>-0.0170141849517822</v>
+      </c>
+      <c r="F77" t="n">
+        <v>-1.025568713187595</v>
       </c>
     </row>
     <row r="78">
@@ -1673,13 +2139,19 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C78" t="n">
+        <v>1.467759132385254</v>
+      </c>
+      <c r="D78" t="n">
         <v>1.471</v>
       </c>
-      <c r="D78" t="n">
-        <v>1.472670197486877</v>
+      <c r="E78" t="n">
+        <v>0.003240867614746179</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.2203173089562324</v>
       </c>
     </row>
     <row r="79">
@@ -1689,13 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C79" t="n">
+        <v>2.593242883682251</v>
+      </c>
+      <c r="D79" t="n">
         <v>2.66</v>
       </c>
-      <c r="D79" t="n">
-        <v>2.583139657974243</v>
+      <c r="E79" t="n">
+        <v>0.06675711631774917</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.509666026983051</v>
       </c>
     </row>
     <row r="80">
@@ -1705,13 +2183,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C80" t="n">
+        <v>1.419056296348572</v>
+      </c>
+      <c r="D80" t="n">
         <v>1.402</v>
       </c>
-      <c r="D80" t="n">
-        <v>1.423996806144714</v>
+      <c r="E80" t="n">
+        <v>-0.01705629634857186</v>
+      </c>
+      <c r="F80" t="n">
+        <v>-1.216568926431659</v>
       </c>
     </row>
     <row r="81">
@@ -1721,13 +2205,19 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C81" t="n">
+        <v>1.657684206962585</v>
+      </c>
+      <c r="D81" t="n">
         <v>1.68</v>
       </c>
-      <c r="D81" t="n">
-        <v>1.66799259185791</v>
+      <c r="E81" t="n">
+        <v>0.02231579303741449</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.328321014131815</v>
       </c>
     </row>
     <row r="82">
@@ -1737,13 +2227,19 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C82" t="n">
+        <v>1.921151399612427</v>
+      </c>
+      <c r="D82" t="n">
         <v>1.946</v>
       </c>
-      <c r="D82" t="n">
-        <v>1.936986327171326</v>
+      <c r="E82" t="n">
+        <v>0.02484860038757319</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.276906494736546</v>
       </c>
     </row>
     <row r="83">
@@ -1753,13 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C83" t="n">
+        <v>1.307550072669983</v>
+      </c>
+      <c r="D83" t="n">
         <v>1.316</v>
       </c>
-      <c r="D83" t="n">
-        <v>1.323512673377991</v>
+      <c r="E83" t="n">
+        <v>0.008449927330017148</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.6420917424025188</v>
       </c>
     </row>
     <row r="84">
@@ -1769,13 +2271,19 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C84" t="n">
+        <v>1.43593168258667</v>
+      </c>
+      <c r="D84" t="n">
         <v>1.424</v>
       </c>
-      <c r="D84" t="n">
-        <v>1.43441641330719</v>
+      <c r="E84" t="n">
+        <v>-0.01193168258666999</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-0.8378990580526678</v>
       </c>
     </row>
     <row r="85">
@@ -1785,13 +2293,19 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C85" t="n">
+        <v>1.295265913009644</v>
+      </c>
+      <c r="D85" t="n">
         <v>1.257</v>
       </c>
-      <c r="D85" t="n">
-        <v>1.276313781738281</v>
+      <c r="E85" t="n">
+        <v>-0.03826591300964366</v>
+      </c>
+      <c r="F85" t="n">
+        <v>-3.044225378651047</v>
       </c>
     </row>
     <row r="86">
@@ -1801,13 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C86" t="n">
+        <v>1.067272186279297</v>
+      </c>
+      <c r="D86" t="n">
         <v>0.976</v>
       </c>
-      <c r="D86" t="n">
-        <v>1.074371457099915</v>
+      <c r="E86" t="n">
+        <v>-0.0912721862792969</v>
+      </c>
+      <c r="F86" t="n">
+        <v>-9.35165843025583</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/XGBoost/predictions_afr.xlsx
+++ b/notebooks/XGBoost/predictions_afr.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>СКР_реальный</t>
+          <t>СКР</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -470,16 +470,16 @@
         <v>2023</v>
       </c>
       <c r="C2" t="n">
-        <v>1.361204504966736</v>
+        <v>1.360465407371521</v>
       </c>
       <c r="D2" t="n">
         <v>1.305</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0562045049667359</v>
+        <v>-0.05546540737152106</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.306858618140683</v>
+        <v>-4.250222787089736</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         <v>2023</v>
       </c>
       <c r="C3" t="n">
-        <v>1.460216641426086</v>
+        <v>1.461077094078064</v>
       </c>
       <c r="D3" t="n">
         <v>1.49</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02978335857391357</v>
+        <v>0.02892290592193603</v>
       </c>
       <c r="F3" t="n">
-        <v>1.998883125766011</v>
+        <v>1.94113462563329</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>2023</v>
       </c>
       <c r="C4" t="n">
-        <v>1.519587516784668</v>
+        <v>1.513939142227173</v>
       </c>
       <c r="D4" t="n">
         <v>1.459</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.06058751678466789</v>
+        <v>-0.05493914222717278</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.152674214165037</v>
+        <v>-3.765534079998134</v>
       </c>
     </row>
     <row r="5">
@@ -536,16 +536,16 @@
         <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>1.645257830619812</v>
+        <v>1.63923704624176</v>
       </c>
       <c r="D5" t="n">
         <v>1.635</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.010257830619812</v>
+        <v>-0.004237046241760245</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6273902519762693</v>
+        <v>-0.259146559129067</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         <v>2023</v>
       </c>
       <c r="C6" t="n">
-        <v>1.150643587112427</v>
+        <v>1.155320167541504</v>
       </c>
       <c r="D6" t="n">
         <v>1.123</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02764358711242676</v>
+        <v>-0.03232016754150391</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.46158389246899</v>
+        <v>-2.878020261932672</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         <v>2023</v>
       </c>
       <c r="C7" t="n">
-        <v>1.21263587474823</v>
+        <v>1.200632333755493</v>
       </c>
       <c r="D7" t="n">
         <v>1.19</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02263587474823003</v>
+        <v>-0.01063233375549322</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.902174348590759</v>
+        <v>-0.8934734248313628</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         <v>2023</v>
       </c>
       <c r="C8" t="n">
-        <v>1.148588299751282</v>
+        <v>1.147945761680603</v>
       </c>
       <c r="D8" t="n">
         <v>1.147</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.001588299751281719</v>
+        <v>-0.0009457616806030078</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.138474259048101</v>
+        <v>-0.08245524678317417</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         <v>2023</v>
       </c>
       <c r="C9" t="n">
-        <v>1.161955714225769</v>
+        <v>1.155553817749023</v>
       </c>
       <c r="D9" t="n">
         <v>1.119</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04295571422576905</v>
+        <v>-0.03655381774902344</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.838759090774714</v>
+        <v>-3.266650379716125</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         <v>2023</v>
       </c>
       <c r="C10" t="n">
-        <v>1.434039115905762</v>
+        <v>1.432007074356079</v>
       </c>
       <c r="D10" t="n">
         <v>1.391</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0430391159057617</v>
+        <v>-0.04100707435607909</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.094113293009468</v>
+        <v>-2.948028350544866</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         <v>2023</v>
       </c>
       <c r="C11" t="n">
-        <v>1.245630741119385</v>
+        <v>1.251051068305969</v>
       </c>
       <c r="D11" t="n">
         <v>1.222</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02363074111938479</v>
+        <v>-0.02905106830596926</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.933775869016759</v>
+        <v>-2.377337831912378</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         <v>2023</v>
       </c>
       <c r="C12" t="n">
-        <v>1.627184987068176</v>
+        <v>1.630135655403137</v>
       </c>
       <c r="D12" t="n">
         <v>1.559</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06818498706817633</v>
+        <v>-0.07113565540313727</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.373636117265961</v>
+        <v>-4.56290284818071</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         <v>2023</v>
       </c>
       <c r="C13" t="n">
-        <v>1.64634895324707</v>
+        <v>1.640939831733704</v>
       </c>
       <c r="D13" t="n">
         <v>1.548</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.09834895324707027</v>
+        <v>-0.09293983173370357</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.353291553428312</v>
+        <v>-6.003865099076458</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         <v>2023</v>
       </c>
       <c r="C14" t="n">
-        <v>1.387126922607422</v>
+        <v>1.379490971565247</v>
       </c>
       <c r="D14" t="n">
         <v>1.346</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04112692260742179</v>
+        <v>-0.0334909715652465</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.055492021353773</v>
+        <v>-2.488185108859324</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         <v>2023</v>
       </c>
       <c r="C15" t="n">
-        <v>1.707546591758728</v>
+        <v>1.703119397163391</v>
       </c>
       <c r="D15" t="n">
         <v>1.65</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05754659175872812</v>
+        <v>-0.0531193971633912</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.487672227801704</v>
+        <v>-3.219357403841891</v>
       </c>
     </row>
     <row r="16">
@@ -778,16 +778,16 @@
         <v>2023</v>
       </c>
       <c r="C16" t="n">
-        <v>1.545559525489807</v>
+        <v>1.529161095619202</v>
       </c>
       <c r="D16" t="n">
         <v>1.526</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01955952548980711</v>
+        <v>-0.003161095619201637</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.281751342713441</v>
+        <v>-0.2071491231455857</v>
       </c>
     </row>
     <row r="17">
@@ -800,16 +800,16 @@
         <v>2023</v>
       </c>
       <c r="C17" t="n">
-        <v>1.275659441947937</v>
+        <v>1.254860997200012</v>
       </c>
       <c r="D17" t="n">
         <v>1.183</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.09265944194793696</v>
+        <v>-0.07186099720001216</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.832581736934655</v>
+        <v>-6.074471445478626</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         <v>2023</v>
       </c>
       <c r="C18" t="n">
-        <v>1.334794163703918</v>
+        <v>1.329731941223145</v>
       </c>
       <c r="D18" t="n">
         <v>1.339</v>
       </c>
       <c r="E18" t="n">
-        <v>0.004205836296081511</v>
+        <v>0.009268058776855437</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3141027853682981</v>
+        <v>0.6921627167181058</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         <v>2023</v>
       </c>
       <c r="C19" t="n">
-        <v>1.630613923072815</v>
+        <v>1.633232116699219</v>
       </c>
       <c r="D19" t="n">
         <v>1.666</v>
       </c>
       <c r="E19" t="n">
-        <v>0.03538607692718498</v>
+        <v>0.03276788330078118</v>
       </c>
       <c r="F19" t="n">
-        <v>2.124014221319627</v>
+        <v>1.966859741943648</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         <v>2023</v>
       </c>
       <c r="C20" t="n">
-        <v>1.30300498008728</v>
+        <v>1.305606245994568</v>
       </c>
       <c r="D20" t="n">
         <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>0.03699501991271981</v>
+        <v>0.03439375400543221</v>
       </c>
       <c r="F20" t="n">
-        <v>2.760822381546254</v>
+        <v>2.566698060106881</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         <v>2023</v>
       </c>
       <c r="C21" t="n">
-        <v>1.301377654075623</v>
+        <v>1.300881147384644</v>
       </c>
       <c r="D21" t="n">
         <v>1.221</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08037765407562247</v>
+        <v>-0.07988114738464347</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.582936451729932</v>
+        <v>-6.542272513074813</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         <v>2023</v>
       </c>
       <c r="C22" t="n">
-        <v>1.521060109138489</v>
+        <v>1.529284238815308</v>
       </c>
       <c r="D22" t="n">
         <v>1.473</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.04806010913848868</v>
+        <v>-0.05628423881530753</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.262736533502286</v>
+        <v>-3.821061698255773</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         <v>2023</v>
       </c>
       <c r="C23" t="n">
-        <v>1.531676054000854</v>
+        <v>1.540991425514221</v>
       </c>
       <c r="D23" t="n">
         <v>1.552</v>
       </c>
       <c r="E23" t="n">
-        <v>0.02032394599914555</v>
+        <v>0.01100857448577885</v>
       </c>
       <c r="F23" t="n">
-        <v>1.309532603037729</v>
+        <v>0.7093153663517303</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         <v>2023</v>
       </c>
       <c r="C24" t="n">
-        <v>1.53467059135437</v>
+        <v>1.540300846099854</v>
       </c>
       <c r="D24" t="n">
         <v>1.532</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.002670591354370089</v>
+        <v>-0.008300846099853487</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1743205844889092</v>
+        <v>-0.5418306853690266</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         <v>2023</v>
       </c>
       <c r="C25" t="n">
-        <v>1.434890627861023</v>
+        <v>1.435121536254883</v>
       </c>
       <c r="D25" t="n">
         <v>1.436</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001109372138976994</v>
+        <v>0.0008784637451171307</v>
       </c>
       <c r="F25" t="n">
-        <v>0.07725432722681017</v>
+        <v>0.06117435550954949</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         <v>2023</v>
       </c>
       <c r="C26" t="n">
-        <v>1.725212931632996</v>
+        <v>1.725730776786804</v>
       </c>
       <c r="D26" t="n">
         <v>1.642</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0832129316329957</v>
+        <v>-0.0837307767868043</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.067779027588045</v>
+        <v>-5.09931649127919</v>
       </c>
     </row>
     <row r="27">
@@ -1020,16 +1020,16 @@
         <v>2023</v>
       </c>
       <c r="C27" t="n">
-        <v>1.304234385490417</v>
+        <v>1.298741340637207</v>
       </c>
       <c r="D27" t="n">
         <v>1.262</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.04223438549041747</v>
+        <v>-0.03674134063720702</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.346623255976028</v>
+        <v>-2.911358212140017</v>
       </c>
     </row>
     <row r="28">
@@ -1042,16 +1042,16 @@
         <v>2023</v>
       </c>
       <c r="C28" t="n">
-        <v>1.004217386245728</v>
+        <v>1.031953573226929</v>
       </c>
       <c r="D28" t="n">
         <v>0.88</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1242173862457275</v>
+        <v>-0.1519535732269287</v>
       </c>
       <c r="F28" t="n">
-        <v>-14.11561207337813</v>
+        <v>-17.26745150306008</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>1.200892806053162</v>
+        <v>1.201615929603577</v>
       </c>
       <c r="D29" t="n">
         <v>1.233</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03210719394683847</v>
+        <v>0.03138407039642344</v>
       </c>
       <c r="F29" t="n">
-        <v>2.603989776710338</v>
+        <v>2.545342286814553</v>
       </c>
     </row>
     <row r="30">
@@ -1086,16 +1086,16 @@
         <v>2023</v>
       </c>
       <c r="C30" t="n">
-        <v>1.434365153312683</v>
+        <v>1.435114979743958</v>
       </c>
       <c r="D30" t="n">
         <v>1.34</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.09436515331268303</v>
+        <v>-0.09511497974395744</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.04217562034948</v>
+        <v>-7.098132816713242</v>
       </c>
     </row>
     <row r="31">
@@ -1108,16 +1108,16 @@
         <v>2023</v>
       </c>
       <c r="C31" t="n">
-        <v>1.32475483417511</v>
+        <v>1.304430603981018</v>
       </c>
       <c r="D31" t="n">
         <v>1.352</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02724516582489023</v>
+        <v>0.04756939601898202</v>
       </c>
       <c r="F31" t="n">
-        <v>2.015174987048094</v>
+        <v>3.518446451108138</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         <v>2023</v>
       </c>
       <c r="C32" t="n">
-        <v>1.46932852268219</v>
+        <v>1.470630884170532</v>
       </c>
       <c r="D32" t="n">
         <v>1.451</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.01832852268218987</v>
+        <v>-0.01963088417053216</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.26316489884148</v>
+        <v>-1.35292103173895</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         <v>2023</v>
       </c>
       <c r="C33" t="n">
-        <v>1.854299187660217</v>
+        <v>1.847373604774475</v>
       </c>
       <c r="D33" t="n">
         <v>1.913</v>
       </c>
       <c r="E33" t="n">
-        <v>0.05870081233978275</v>
+        <v>0.06562639522552494</v>
       </c>
       <c r="F33" t="n">
-        <v>3.068521293245309</v>
+        <v>3.430548626530316</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         <v>2023</v>
       </c>
       <c r="C34" t="n">
-        <v>1.310773253440857</v>
+        <v>1.316365599632263</v>
       </c>
       <c r="D34" t="n">
         <v>1.309</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.001773253440856992</v>
+        <v>-0.007365599632263242</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1354662674451484</v>
+        <v>-0.5626890475372989</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         <v>2023</v>
       </c>
       <c r="C35" t="n">
-        <v>1.320708632469177</v>
+        <v>1.330850720405579</v>
       </c>
       <c r="D35" t="n">
         <v>1.257</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.06370863246917735</v>
+        <v>-0.07385072040557872</v>
       </c>
       <c r="F35" t="n">
-        <v>-5.068308072329145</v>
+        <v>-5.875156754620424</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         <v>2023</v>
       </c>
       <c r="C36" t="n">
-        <v>1.520466685295105</v>
+        <v>1.512302756309509</v>
       </c>
       <c r="D36" t="n">
         <v>1.492</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.02846668529510499</v>
+        <v>-0.02030275630950928</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.907954778492291</v>
+        <v>-1.360774551575689</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2023</v>
       </c>
       <c r="C37" t="n">
-        <v>1.536909341812134</v>
+        <v>1.538889527320862</v>
       </c>
       <c r="D37" t="n">
         <v>1.495</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.04190934181213368</v>
+        <v>-0.04388952732086171</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.803300455661116</v>
+        <v>-2.935754335843592</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         <v>2023</v>
       </c>
       <c r="C38" t="n">
-        <v>1.484651327133179</v>
+        <v>1.481043457984924</v>
       </c>
       <c r="D38" t="n">
         <v>1.502</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01734867286682129</v>
+        <v>0.02095654201507569</v>
       </c>
       <c r="F38" t="n">
-        <v>1.155038140267729</v>
+        <v>1.395242477701444</v>
       </c>
     </row>
     <row r="39">
@@ -1284,16 +1284,16 @@
         <v>2023</v>
       </c>
       <c r="C39" t="n">
-        <v>1.232507824897766</v>
+        <v>1.226033329963684</v>
       </c>
       <c r="D39" t="n">
         <v>1.171</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.06150782489776607</v>
+        <v>-0.05503332996368404</v>
       </c>
       <c r="F39" t="n">
-        <v>-5.252589658220843</v>
+        <v>-4.699686589554572</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         <v>2023</v>
       </c>
       <c r="C40" t="n">
-        <v>1.203209638595581</v>
+        <v>1.203783392906189</v>
       </c>
       <c r="D40" t="n">
         <v>1.198</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.005209638595581101</v>
+        <v>-0.005783392906189011</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.4348613184959183</v>
+        <v>-0.4827539988471629</v>
       </c>
     </row>
     <row r="41">
@@ -1328,16 +1328,16 @@
         <v>2023</v>
       </c>
       <c r="C41" t="n">
-        <v>1.550869822502136</v>
+        <v>1.559928894042969</v>
       </c>
       <c r="D41" t="n">
         <v>1.527</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.02386982250213632</v>
+        <v>-0.03292889404296884</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.563184184815738</v>
+        <v>-2.156443617745176</v>
       </c>
     </row>
     <row r="42">
@@ -1350,16 +1350,16 @@
         <v>2023</v>
       </c>
       <c r="C42" t="n">
-        <v>1.439392805099487</v>
+        <v>1.443645119667053</v>
       </c>
       <c r="D42" t="n">
         <v>1.444</v>
       </c>
       <c r="E42" t="n">
-        <v>0.004607194900512646</v>
+        <v>0.0003548803329467276</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3190578185950586</v>
+        <v>0.02457620034257117</v>
       </c>
     </row>
     <row r="43">
@@ -1372,16 +1372,16 @@
         <v>2023</v>
       </c>
       <c r="C43" t="n">
-        <v>1.362046122550964</v>
+        <v>1.352548599243164</v>
       </c>
       <c r="D43" t="n">
         <v>1.305</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.05704612255096442</v>
+        <v>-0.04754859924316412</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.371350387047082</v>
+        <v>-3.643570823230967</v>
       </c>
     </row>
     <row r="44">
@@ -1394,16 +1394,16 @@
         <v>2023</v>
       </c>
       <c r="C44" t="n">
-        <v>1.320439338684082</v>
+        <v>1.310077667236328</v>
       </c>
       <c r="D44" t="n">
         <v>1.346</v>
       </c>
       <c r="E44" t="n">
-        <v>0.02556066131591805</v>
+        <v>0.03592233276367196</v>
       </c>
       <c r="F44" t="n">
-        <v>1.899009013069692</v>
+        <v>2.668821156290636</v>
       </c>
     </row>
     <row r="45">
@@ -1416,16 +1416,16 @@
         <v>2023</v>
       </c>
       <c r="C45" t="n">
-        <v>2.07588791847229</v>
+        <v>2.048995971679688</v>
       </c>
       <c r="D45" t="n">
         <v>2.03</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.04588791847229023</v>
+        <v>-0.0189959716796877</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.2604885946941</v>
+        <v>-0.9357621517087535</v>
       </c>
     </row>
     <row r="46">
@@ -1438,16 +1438,16 @@
         <v>2023</v>
       </c>
       <c r="C46" t="n">
-        <v>1.410475373268127</v>
+        <v>1.422918796539307</v>
       </c>
       <c r="D46" t="n">
         <v>1.414</v>
       </c>
       <c r="E46" t="n">
-        <v>0.003524626731872482</v>
+        <v>-0.008918796539306717</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2492663883926791</v>
+        <v>-0.6307494016482826</v>
       </c>
     </row>
     <row r="47">
@@ -1460,16 +1460,16 @@
         <v>2023</v>
       </c>
       <c r="C47" t="n">
-        <v>1.722460508346558</v>
+        <v>1.717650175094604</v>
       </c>
       <c r="D47" t="n">
         <v>1.597</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1254605083465576</v>
+        <v>-0.1206501750946045</v>
       </c>
       <c r="F47" t="n">
-        <v>-7.856011793773178</v>
+        <v>-7.554801195654635</v>
       </c>
     </row>
     <row r="48">
@@ -1482,16 +1482,16 @@
         <v>2023</v>
       </c>
       <c r="C48" t="n">
-        <v>1.749882102012634</v>
+        <v>1.742419838905334</v>
       </c>
       <c r="D48" t="n">
         <v>1.745</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.004882102012634171</v>
+        <v>0.002580161094665634</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.279776619635196</v>
+        <v>0.1478602346513257</v>
       </c>
     </row>
     <row r="49">
@@ -1504,16 +1504,16 @@
         <v>2023</v>
       </c>
       <c r="C49" t="n">
-        <v>1.837307810783386</v>
+        <v>1.839191317558289</v>
       </c>
       <c r="D49" t="n">
         <v>1.806</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.03130781078338618</v>
+        <v>-0.03319131755828852</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.733544340165348</v>
+        <v>-1.837835966682642</v>
       </c>
     </row>
     <row r="50">
@@ -1526,16 +1526,16 @@
         <v>2023</v>
       </c>
       <c r="C50" t="n">
-        <v>1.434138298034668</v>
+        <v>1.422760367393494</v>
       </c>
       <c r="D50" t="n">
         <v>1.443</v>
       </c>
       <c r="E50" t="n">
-        <v>0.008861701965332092</v>
+        <v>0.02023963260650641</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6141165603140742</v>
+        <v>1.402607942238836</v>
       </c>
     </row>
     <row r="51">
@@ -1548,16 +1548,16 @@
         <v>2023</v>
       </c>
       <c r="C51" t="n">
-        <v>1.539367079734802</v>
+        <v>1.54428505897522</v>
       </c>
       <c r="D51" t="n">
         <v>1.534</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.005367079734802216</v>
+        <v>-0.0102850589752197</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.3498748197393882</v>
+        <v>-0.670473205685769</v>
       </c>
     </row>
     <row r="52">
@@ -1570,16 +1570,16 @@
         <v>2023</v>
       </c>
       <c r="C52" t="n">
-        <v>1.557774901390076</v>
+        <v>1.564611673355103</v>
       </c>
       <c r="D52" t="n">
         <v>1.564</v>
       </c>
       <c r="E52" t="n">
-        <v>0.006225098609924373</v>
+        <v>-0.0006116733551024822</v>
       </c>
       <c r="F52" t="n">
-        <v>0.398024207795676</v>
+        <v>-0.03910954955898224</v>
       </c>
     </row>
     <row r="53">
@@ -1592,16 +1592,16 @@
         <v>2023</v>
       </c>
       <c r="C53" t="n">
-        <v>1.437110424041748</v>
+        <v>1.43991494178772</v>
       </c>
       <c r="D53" t="n">
         <v>1.419</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.01811042404174801</v>
+        <v>-0.02091494178771969</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.276280764041438</v>
+        <v>-1.473921197161359</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         <v>2023</v>
       </c>
       <c r="C54" t="n">
-        <v>1.435223817825317</v>
+        <v>1.439913272857666</v>
       </c>
       <c r="D54" t="n">
         <v>1.381</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.05422381782531738</v>
+        <v>-0.05891327285766601</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.926416931594306</v>
+        <v>-4.265986448781029</v>
       </c>
     </row>
     <row r="55">
@@ -1636,16 +1636,16 @@
         <v>2023</v>
       </c>
       <c r="C55" t="n">
-        <v>1.095302581787109</v>
+        <v>1.059122800827026</v>
       </c>
       <c r="D55" t="n">
         <v>1.047</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.04830258178710944</v>
+        <v>-0.01212280082702644</v>
       </c>
       <c r="F55" t="n">
-        <v>-4.613427104786003</v>
+        <v>-1.157860632953815</v>
       </c>
     </row>
     <row r="56">
@@ -1658,16 +1658,16 @@
         <v>2023</v>
       </c>
       <c r="C56" t="n">
-        <v>1.7225261926651</v>
+        <v>1.721526980400085</v>
       </c>
       <c r="D56" t="n">
         <v>1.619</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.1035261926651001</v>
+        <v>-0.1025269804000855</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.394452913224219</v>
+        <v>-6.33273504633017</v>
       </c>
     </row>
     <row r="57">
@@ -1680,16 +1680,16 @@
         <v>2023</v>
       </c>
       <c r="C57" t="n">
-        <v>1.595932722091675</v>
+        <v>1.604254126548767</v>
       </c>
       <c r="D57" t="n">
         <v>1.52</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.07593272209167479</v>
+        <v>-0.08425412654876707</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.99557382182071</v>
+        <v>-5.543034641366255</v>
       </c>
     </row>
     <row r="58">
@@ -1702,16 +1702,16 @@
         <v>2023</v>
       </c>
       <c r="C58" t="n">
-        <v>1.431061983108521</v>
+        <v>1.430442571640015</v>
       </c>
       <c r="D58" t="n">
         <v>1.454</v>
       </c>
       <c r="E58" t="n">
-        <v>0.02293801689147945</v>
+        <v>0.02355742835998531</v>
       </c>
       <c r="F58" t="n">
-        <v>1.577580253884419</v>
+        <v>1.620180767536817</v>
       </c>
     </row>
     <row r="59">
@@ -1724,16 +1724,16 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>2.456992149353027</v>
+        <v>2.480222702026367</v>
       </c>
       <c r="D59" t="n">
         <v>2.442</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.01499214935302717</v>
+        <v>-0.03822270202636702</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6139291299355926</v>
+        <v>-1.565221213200942</v>
       </c>
     </row>
     <row r="60">
@@ -1746,16 +1746,16 @@
         <v>2023</v>
       </c>
       <c r="C60" t="n">
-        <v>1.56514573097229</v>
+        <v>1.554483294487</v>
       </c>
       <c r="D60" t="n">
         <v>1.522</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.04314573097229002</v>
+        <v>-0.03248329448699949</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.834804925906046</v>
+        <v>-2.13425062332454</v>
       </c>
     </row>
     <row r="61">
@@ -1768,16 +1768,16 @@
         <v>2023</v>
       </c>
       <c r="C61" t="n">
-        <v>1.311789035797119</v>
+        <v>1.276632785797119</v>
       </c>
       <c r="D61" t="n">
         <v>1.272</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.03978903579711912</v>
+        <v>-0.004632785797119121</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.128068851974774</v>
+        <v>-0.364212719899302</v>
       </c>
     </row>
     <row r="62">
@@ -1790,16 +1790,16 @@
         <v>2023</v>
       </c>
       <c r="C62" t="n">
-        <v>1.155730843544006</v>
+        <v>1.153620719909668</v>
       </c>
       <c r="D62" t="n">
         <v>1.104</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.05173084354400626</v>
+        <v>-0.04962071990966788</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.685764813768682</v>
+        <v>-4.494630426600351</v>
       </c>
     </row>
     <row r="63">
@@ -1812,16 +1812,16 @@
         <v>2023</v>
       </c>
       <c r="C63" t="n">
-        <v>1.319729685783386</v>
+        <v>1.337128877639771</v>
       </c>
       <c r="D63" t="n">
         <v>1.33</v>
       </c>
       <c r="E63" t="n">
-        <v>0.01027031421661384</v>
+        <v>-0.007128877639770437</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7722040764371307</v>
+        <v>-0.5360058375767246</v>
       </c>
     </row>
     <row r="64">
@@ -1834,16 +1834,16 @@
         <v>2023</v>
       </c>
       <c r="C64" t="n">
-        <v>1.121143698692322</v>
+        <v>1.123972654342651</v>
       </c>
       <c r="D64" t="n">
         <v>1.103</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.0181436986923218</v>
+        <v>-0.02097265434265139</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.644940951253109</v>
+        <v>-1.901419251373653</v>
       </c>
     </row>
     <row r="65">
@@ -1856,16 +1856,16 @@
         <v>2023</v>
       </c>
       <c r="C65" t="n">
-        <v>1.777756690979004</v>
+        <v>1.782228112220764</v>
       </c>
       <c r="D65" t="n">
         <v>1.736</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.04175669097900392</v>
+        <v>-0.04622811222076417</v>
       </c>
       <c r="F65" t="n">
-        <v>-2.405339342108521</v>
+        <v>-2.662909690136185</v>
       </c>
     </row>
     <row r="66">
@@ -1878,16 +1878,16 @@
         <v>2023</v>
       </c>
       <c r="C66" t="n">
-        <v>1.563356518745422</v>
+        <v>1.563187837600708</v>
       </c>
       <c r="D66" t="n">
         <v>1.551</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.01235651874542243</v>
+        <v>-0.01218783760070807</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7966807701755273</v>
+        <v>-0.7858051322184445</v>
       </c>
     </row>
     <row r="67">
@@ -1900,16 +1900,16 @@
         <v>2023</v>
       </c>
       <c r="C67" t="n">
-        <v>1.096142530441284</v>
+        <v>1.096610903739929</v>
       </c>
       <c r="D67" t="n">
         <v>1.033</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.06314253044128426</v>
+        <v>-0.06361090373992928</v>
       </c>
       <c r="F67" t="n">
-        <v>-6.112539248914256</v>
+        <v>-6.157880323323261</v>
       </c>
     </row>
     <row r="68">
@@ -1922,16 +1922,16 @@
         <v>2023</v>
       </c>
       <c r="C68" t="n">
-        <v>1.28760302066803</v>
+        <v>1.28560197353363</v>
       </c>
       <c r="D68" t="n">
         <v>1.297</v>
       </c>
       <c r="E68" t="n">
-        <v>0.009396979331970146</v>
+        <v>0.01139802646636956</v>
       </c>
       <c r="F68" t="n">
-        <v>0.724516525209726</v>
+        <v>0.8787992649475375</v>
       </c>
     </row>
     <row r="69">
@@ -1944,16 +1944,16 @@
         <v>2023</v>
       </c>
       <c r="C69" t="n">
-        <v>1.228188633918762</v>
+        <v>1.229712247848511</v>
       </c>
       <c r="D69" t="n">
         <v>1.207</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.02118863391876213</v>
+        <v>-0.02271224784851067</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.755479197909042</v>
+        <v>-1.881710675104446</v>
       </c>
     </row>
     <row r="70">
@@ -1966,16 +1966,16 @@
         <v>2023</v>
       </c>
       <c r="C70" t="n">
-        <v>1.303571343421936</v>
+        <v>1.303176045417786</v>
       </c>
       <c r="D70" t="n">
         <v>1.278</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.02557134342193601</v>
+        <v>-0.02517604541778562</v>
       </c>
       <c r="F70" t="n">
-        <v>-2.000887591700783</v>
+        <v>-1.969956605460534</v>
       </c>
     </row>
     <row r="71">
@@ -1988,16 +1988,16 @@
         <v>2023</v>
       </c>
       <c r="C71" t="n">
-        <v>1.244389057159424</v>
+        <v>1.245118856430054</v>
       </c>
       <c r="D71" t="n">
         <v>1.189</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.05538905715942377</v>
+        <v>-0.05611885643005365</v>
       </c>
       <c r="F71" t="n">
-        <v>-4.658457288429249</v>
+        <v>-4.719836537430921</v>
       </c>
     </row>
     <row r="72">
@@ -2010,16 +2010,16 @@
         <v>2023</v>
       </c>
       <c r="C72" t="n">
-        <v>1.160467624664307</v>
+        <v>1.143359661102295</v>
       </c>
       <c r="D72" t="n">
         <v>1.179</v>
       </c>
       <c r="E72" t="n">
-        <v>0.01853237533569341</v>
+        <v>0.03564033889770513</v>
       </c>
       <c r="F72" t="n">
-        <v>1.571872377921409</v>
+        <v>3.02292950786303</v>
       </c>
     </row>
     <row r="73">
@@ -2032,16 +2032,16 @@
         <v>2023</v>
       </c>
       <c r="C73" t="n">
-        <v>1.719456434249878</v>
+        <v>1.719090819358826</v>
       </c>
       <c r="D73" t="n">
         <v>1.72</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0005435657501220437</v>
+        <v>0.0009091806411742898</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0316026598908165</v>
+        <v>0.05285933960315638</v>
       </c>
     </row>
     <row r="74">
@@ -2054,16 +2054,16 @@
         <v>2023</v>
       </c>
       <c r="C74" t="n">
-        <v>1.440039277076721</v>
+        <v>1.44277024269104</v>
       </c>
       <c r="D74" t="n">
         <v>1.399</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.04103927707672117</v>
+        <v>-0.04377024269104002</v>
       </c>
       <c r="F74" t="n">
-        <v>-2.933472271388218</v>
+        <v>-3.128680678416012</v>
       </c>
     </row>
     <row r="75">
@@ -2076,16 +2076,16 @@
         <v>2023</v>
       </c>
       <c r="C75" t="n">
-        <v>1.358943343162537</v>
+        <v>1.336506605148315</v>
       </c>
       <c r="D75" t="n">
         <v>1.34</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.01894334316253654</v>
+        <v>0.00349339485168465</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.413682325562428</v>
+        <v>0.2607011083346754</v>
       </c>
     </row>
     <row r="76">
@@ -2098,16 +2098,16 @@
         <v>2023</v>
       </c>
       <c r="C76" t="n">
-        <v>1.527583003044128</v>
+        <v>1.527649879455566</v>
       </c>
       <c r="D76" t="n">
         <v>1.463</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.06458300304412834</v>
+        <v>-0.06464987945556633</v>
       </c>
       <c r="F76" t="n">
-        <v>-4.414422627759969</v>
+        <v>-4.418993811043494</v>
       </c>
     </row>
     <row r="77">
@@ -2120,16 +2120,16 @@
         <v>2023</v>
       </c>
       <c r="C77" t="n">
-        <v>1.676014184951782</v>
+        <v>1.679227948188782</v>
       </c>
       <c r="D77" t="n">
         <v>1.659</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.0170141849517822</v>
+        <v>-0.02022794818878171</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.025568713187595</v>
+        <v>-1.21928560511041</v>
       </c>
     </row>
     <row r="78">
@@ -2142,16 +2142,16 @@
         <v>2023</v>
       </c>
       <c r="C78" t="n">
-        <v>1.467759132385254</v>
+        <v>1.460740327835083</v>
       </c>
       <c r="D78" t="n">
         <v>1.471</v>
       </c>
       <c r="E78" t="n">
-        <v>0.003240867614746179</v>
+        <v>0.01025967216491708</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2203173089562324</v>
+        <v>0.6974624177373947</v>
       </c>
     </row>
     <row r="79">
@@ -2164,16 +2164,16 @@
         <v>2023</v>
       </c>
       <c r="C79" t="n">
-        <v>2.593242883682251</v>
+        <v>2.607785701751709</v>
       </c>
       <c r="D79" t="n">
         <v>2.66</v>
       </c>
       <c r="E79" t="n">
-        <v>0.06675711631774917</v>
+        <v>0.05221429824829116</v>
       </c>
       <c r="F79" t="n">
-        <v>2.509666026983051</v>
+        <v>1.96294354316884</v>
       </c>
     </row>
     <row r="80">
@@ -2186,16 +2186,16 @@
         <v>2023</v>
       </c>
       <c r="C80" t="n">
-        <v>1.419056296348572</v>
+        <v>1.43105161190033</v>
       </c>
       <c r="D80" t="n">
         <v>1.402</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.01705629634857186</v>
+        <v>-0.02905161190032968</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.216568926431659</v>
+        <v>-2.072154914431503</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2023</v>
       </c>
       <c r="C81" t="n">
-        <v>1.657684206962585</v>
+        <v>1.664395332336426</v>
       </c>
       <c r="D81" t="n">
         <v>1.68</v>
       </c>
       <c r="E81" t="n">
-        <v>0.02231579303741449</v>
+        <v>0.01560466766357416</v>
       </c>
       <c r="F81" t="n">
-        <v>1.328321014131815</v>
+        <v>0.9288492656889379</v>
       </c>
     </row>
     <row r="82">
@@ -2230,16 +2230,16 @@
         <v>2023</v>
       </c>
       <c r="C82" t="n">
-        <v>1.921151399612427</v>
+        <v>1.91675853729248</v>
       </c>
       <c r="D82" t="n">
         <v>1.946</v>
       </c>
       <c r="E82" t="n">
-        <v>0.02484860038757319</v>
+        <v>0.02924146270751948</v>
       </c>
       <c r="F82" t="n">
-        <v>1.276906494736546</v>
+        <v>1.502644537899254</v>
       </c>
     </row>
     <row r="83">
@@ -2252,16 +2252,16 @@
         <v>2023</v>
       </c>
       <c r="C83" t="n">
-        <v>1.307550072669983</v>
+        <v>1.33993124961853</v>
       </c>
       <c r="D83" t="n">
         <v>1.316</v>
       </c>
       <c r="E83" t="n">
-        <v>0.008449927330017148</v>
+        <v>-0.02393124961853021</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6420917424025188</v>
+        <v>-1.818484013566126</v>
       </c>
     </row>
     <row r="84">
@@ -2274,16 +2274,16 @@
         <v>2023</v>
       </c>
       <c r="C84" t="n">
-        <v>1.43593168258667</v>
+        <v>1.42740261554718</v>
       </c>
       <c r="D84" t="n">
         <v>1.424</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.01193168258666999</v>
+        <v>-0.003402615547180243</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.8378990580526678</v>
+        <v>-0.2389477210098486</v>
       </c>
     </row>
     <row r="85">
@@ -2296,16 +2296,16 @@
         <v>2023</v>
       </c>
       <c r="C85" t="n">
-        <v>1.295265913009644</v>
+        <v>1.289276957511902</v>
       </c>
       <c r="D85" t="n">
         <v>1.257</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.03826591300964366</v>
+        <v>-0.03227695751190196</v>
       </c>
       <c r="F85" t="n">
-        <v>-3.044225378651047</v>
+        <v>-2.567777049475096</v>
       </c>
     </row>
     <row r="86">
@@ -2318,16 +2318,16 @@
         <v>2023</v>
       </c>
       <c r="C86" t="n">
-        <v>1.067272186279297</v>
+        <v>1.080246686935425</v>
       </c>
       <c r="D86" t="n">
         <v>0.976</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.0912721862792969</v>
+        <v>-0.1042466869354248</v>
       </c>
       <c r="F86" t="n">
-        <v>-9.35165843025583</v>
+        <v>-10.68101300567877</v>
       </c>
     </row>
   </sheetData>
